--- a/sample-project2/srcs/CSharp_ASPNET/build/test-results/independent-browser/literal-career.xlsx
+++ b/sample-project2/srcs/CSharp_ASPNET/build/test-results/independent-browser/literal-career.xlsx
@@ -26,7 +26,7 @@
     <x:t>2026年10月29日現在</x:t>
   </x:si>
   <x:si>
-    <x:t>作成日時（JST）：2026年10月29日 01:05</x:t>
+    <x:t>作成日時（JST）：2026年10月29日 14:12</x:t>
   </x:si>
   <x:si>
     <x:t>氏名</x:t>
@@ -38,7 +38,7 @@
     <x:t>社員番号・所属</x:t>
   </x:si>
   <x:si>
-    <x:t>000006 ／ 開発</x:t>
+    <x:t>000004 ／ 開発</x:t>
   </x:si>
   <x:si>
     <x:t>職務要約</x:t>
@@ -141,7 +141,7 @@
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="10.5"/>
-      <x:color rgb="FF000000"/>
+      <x:color rgb="FF202B38"/>
       <x:name val="Meiryo"/>
       <x:family val="2"/>
     </x:font>
@@ -149,7 +149,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
-      <x:color rgb="FF000000"/>
+      <x:color rgb="FF173650"/>
       <x:name val="Meiryo"/>
       <x:family val="2"/>
     </x:font>
@@ -157,20 +157,25 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
+      <x:color rgb="FF173650"/>
       <x:name val="Meiryo"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="8">
     <x:border diagonalUp="0" diagonalDown="0">
       <x:left style="none">
         <x:color rgb="FF000000"/>
@@ -183,54 +188,215 @@
       </x:top>
       <x:bottom style="none">
         <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF173650"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF173650"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF173650"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF173650"/>
       </x:bottom>
       <x:diagonal style="none">
         <x:color rgb="FF000000"/>
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="2" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="3" fillId="2" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="3" fillId="2" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -554,49 +720,93 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A5" s="3" t="s">
+      <x:c r="A5" s="4" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="s">
+      <x:c r="B5" s="5"/>
+      <x:c r="C5" s="5"/>
+      <x:c r="D5" s="5"/>
+      <x:c r="E5" s="5"/>
+      <x:c r="F5" s="6"/>
+      <x:c r="G5" s="4" t="s">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="H5" s="5"/>
+      <x:c r="I5" s="5"/>
+      <x:c r="J5" s="5"/>
+      <x:c r="K5" s="5"/>
+      <x:c r="L5" s="5"/>
+      <x:c r="M5" s="5"/>
+      <x:c r="N5" s="5"/>
+      <x:c r="O5" s="5"/>
+      <x:c r="P5" s="5"/>
+      <x:c r="Q5" s="5"/>
+      <x:c r="R5" s="5"/>
+      <x:c r="S5" s="5"/>
+      <x:c r="T5" s="5"/>
+      <x:c r="U5" s="5"/>
+      <x:c r="V5" s="5"/>
+      <x:c r="W5" s="5"/>
+      <x:c r="X5" s="6"/>
     </x:row>
     <x:row r="6" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A6" s="3" t="s">
+      <x:c r="A6" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="s">
+      <x:c r="B6" s="5"/>
+      <x:c r="C6" s="5"/>
+      <x:c r="D6" s="5"/>
+      <x:c r="E6" s="5"/>
+      <x:c r="F6" s="6"/>
+      <x:c r="G6" s="4" t="s">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="H6" s="5"/>
+      <x:c r="I6" s="5"/>
+      <x:c r="J6" s="5"/>
+      <x:c r="K6" s="5"/>
+      <x:c r="L6" s="5"/>
+      <x:c r="M6" s="5"/>
+      <x:c r="N6" s="5"/>
+      <x:c r="O6" s="5"/>
+      <x:c r="P6" s="5"/>
+      <x:c r="Q6" s="5"/>
+      <x:c r="R6" s="5"/>
+      <x:c r="S6" s="5"/>
+      <x:c r="T6" s="5"/>
+      <x:c r="U6" s="5"/>
+      <x:c r="V6" s="5"/>
+      <x:c r="W6" s="5"/>
+      <x:c r="X6" s="6"/>
     </x:row>
     <x:row r="7" spans="1:24" ht="15" customHeight="1"/>
     <x:row r="8" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A8" s="4" t="s">
+      <x:c r="A8" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B8" s="5"/>
-      <x:c r="C8" s="5"/>
-      <x:c r="D8" s="5"/>
-      <x:c r="E8" s="5"/>
-      <x:c r="F8" s="5"/>
-      <x:c r="G8" s="5"/>
-      <x:c r="H8" s="5"/>
-      <x:c r="I8" s="5"/>
-      <x:c r="J8" s="5"/>
-      <x:c r="K8" s="5"/>
-      <x:c r="L8" s="5"/>
-      <x:c r="M8" s="5"/>
-      <x:c r="N8" s="5"/>
-      <x:c r="O8" s="5"/>
-      <x:c r="P8" s="5"/>
-      <x:c r="Q8" s="5"/>
-      <x:c r="R8" s="5"/>
-      <x:c r="S8" s="5"/>
-      <x:c r="T8" s="5"/>
-      <x:c r="U8" s="5"/>
-      <x:c r="V8" s="5"/>
-      <x:c r="W8" s="5"/>
-      <x:c r="X8" s="5"/>
+      <x:c r="B8" s="8"/>
+      <x:c r="C8" s="8"/>
+      <x:c r="D8" s="8"/>
+      <x:c r="E8" s="8"/>
+      <x:c r="F8" s="8"/>
+      <x:c r="G8" s="8"/>
+      <x:c r="H8" s="8"/>
+      <x:c r="I8" s="8"/>
+      <x:c r="J8" s="8"/>
+      <x:c r="K8" s="8"/>
+      <x:c r="L8" s="8"/>
+      <x:c r="M8" s="8"/>
+      <x:c r="N8" s="8"/>
+      <x:c r="O8" s="8"/>
+      <x:c r="P8" s="8"/>
+      <x:c r="Q8" s="8"/>
+      <x:c r="R8" s="8"/>
+      <x:c r="S8" s="8"/>
+      <x:c r="T8" s="8"/>
+      <x:c r="U8" s="8"/>
+      <x:c r="V8" s="8"/>
+      <x:c r="W8" s="8"/>
+      <x:c r="X8" s="8"/>
     </x:row>
     <x:row r="9" spans="1:24" ht="15" customHeight="1">
       <x:c r="A9" s="3" t="s">
@@ -610,32 +820,32 @@
     </x:row>
     <x:row r="11" spans="1:24" ht="15" customHeight="1"/>
     <x:row r="12" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A12" s="4" t="s">
+      <x:c r="A12" s="7" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B12" s="5"/>
-      <x:c r="C12" s="5"/>
-      <x:c r="D12" s="5"/>
-      <x:c r="E12" s="5"/>
-      <x:c r="F12" s="5"/>
-      <x:c r="G12" s="5"/>
-      <x:c r="H12" s="5"/>
-      <x:c r="I12" s="5"/>
-      <x:c r="J12" s="5"/>
-      <x:c r="K12" s="5"/>
-      <x:c r="L12" s="5"/>
-      <x:c r="M12" s="5"/>
-      <x:c r="N12" s="5"/>
-      <x:c r="O12" s="5"/>
-      <x:c r="P12" s="5"/>
-      <x:c r="Q12" s="5"/>
-      <x:c r="R12" s="5"/>
-      <x:c r="S12" s="5"/>
-      <x:c r="T12" s="5"/>
-      <x:c r="U12" s="5"/>
-      <x:c r="V12" s="5"/>
-      <x:c r="W12" s="5"/>
-      <x:c r="X12" s="5"/>
+      <x:c r="B12" s="8"/>
+      <x:c r="C12" s="8"/>
+      <x:c r="D12" s="8"/>
+      <x:c r="E12" s="8"/>
+      <x:c r="F12" s="8"/>
+      <x:c r="G12" s="8"/>
+      <x:c r="H12" s="8"/>
+      <x:c r="I12" s="8"/>
+      <x:c r="J12" s="8"/>
+      <x:c r="K12" s="8"/>
+      <x:c r="L12" s="8"/>
+      <x:c r="M12" s="8"/>
+      <x:c r="N12" s="8"/>
+      <x:c r="O12" s="8"/>
+      <x:c r="P12" s="8"/>
+      <x:c r="Q12" s="8"/>
+      <x:c r="R12" s="8"/>
+      <x:c r="S12" s="8"/>
+      <x:c r="T12" s="8"/>
+      <x:c r="U12" s="8"/>
+      <x:c r="V12" s="8"/>
+      <x:c r="W12" s="8"/>
+      <x:c r="X12" s="8"/>
     </x:row>
     <x:row r="13" spans="1:24" ht="15" customHeight="1">
       <x:c r="A13" s="3" t="s">
@@ -644,32 +854,32 @@
     </x:row>
     <x:row r="14" spans="1:24" ht="15" customHeight="1"/>
     <x:row r="15" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A15" s="4" t="s">
+      <x:c r="A15" s="7" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B15" s="5"/>
-      <x:c r="C15" s="5"/>
-      <x:c r="D15" s="5"/>
-      <x:c r="E15" s="5"/>
-      <x:c r="F15" s="5"/>
-      <x:c r="G15" s="5"/>
-      <x:c r="H15" s="5"/>
-      <x:c r="I15" s="5"/>
-      <x:c r="J15" s="5"/>
-      <x:c r="K15" s="5"/>
-      <x:c r="L15" s="5"/>
-      <x:c r="M15" s="5"/>
-      <x:c r="N15" s="5"/>
-      <x:c r="O15" s="5"/>
-      <x:c r="P15" s="5"/>
-      <x:c r="Q15" s="5"/>
-      <x:c r="R15" s="5"/>
-      <x:c r="S15" s="5"/>
-      <x:c r="T15" s="5"/>
-      <x:c r="U15" s="5"/>
-      <x:c r="V15" s="5"/>
-      <x:c r="W15" s="5"/>
-      <x:c r="X15" s="5"/>
+      <x:c r="B15" s="8"/>
+      <x:c r="C15" s="8"/>
+      <x:c r="D15" s="8"/>
+      <x:c r="E15" s="8"/>
+      <x:c r="F15" s="8"/>
+      <x:c r="G15" s="8"/>
+      <x:c r="H15" s="8"/>
+      <x:c r="I15" s="8"/>
+      <x:c r="J15" s="8"/>
+      <x:c r="K15" s="8"/>
+      <x:c r="L15" s="8"/>
+      <x:c r="M15" s="8"/>
+      <x:c r="N15" s="8"/>
+      <x:c r="O15" s="8"/>
+      <x:c r="P15" s="8"/>
+      <x:c r="Q15" s="8"/>
+      <x:c r="R15" s="8"/>
+      <x:c r="S15" s="8"/>
+      <x:c r="T15" s="8"/>
+      <x:c r="U15" s="8"/>
+      <x:c r="V15" s="8"/>
+      <x:c r="W15" s="8"/>
+      <x:c r="X15" s="8"/>
     </x:row>
     <x:row r="16" spans="1:24" ht="15" customHeight="1">
       <x:c r="A16" s="3" t="s">
@@ -678,32 +888,32 @@
     </x:row>
     <x:row r="17" spans="1:24" ht="15" customHeight="1"/>
     <x:row r="18" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A18" s="4" t="s">
+      <x:c r="A18" s="7" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B18" s="5"/>
-      <x:c r="C18" s="5"/>
-      <x:c r="D18" s="5"/>
-      <x:c r="E18" s="5"/>
-      <x:c r="F18" s="5"/>
-      <x:c r="G18" s="5"/>
-      <x:c r="H18" s="5"/>
-      <x:c r="I18" s="5"/>
-      <x:c r="J18" s="5"/>
-      <x:c r="K18" s="5"/>
-      <x:c r="L18" s="5"/>
-      <x:c r="M18" s="5"/>
-      <x:c r="N18" s="5"/>
-      <x:c r="O18" s="5"/>
-      <x:c r="P18" s="5"/>
-      <x:c r="Q18" s="5"/>
-      <x:c r="R18" s="5"/>
-      <x:c r="S18" s="5"/>
-      <x:c r="T18" s="5"/>
-      <x:c r="U18" s="5"/>
-      <x:c r="V18" s="5"/>
-      <x:c r="W18" s="5"/>
-      <x:c r="X18" s="5"/>
+      <x:c r="B18" s="8"/>
+      <x:c r="C18" s="8"/>
+      <x:c r="D18" s="8"/>
+      <x:c r="E18" s="8"/>
+      <x:c r="F18" s="8"/>
+      <x:c r="G18" s="8"/>
+      <x:c r="H18" s="8"/>
+      <x:c r="I18" s="8"/>
+      <x:c r="J18" s="8"/>
+      <x:c r="K18" s="8"/>
+      <x:c r="L18" s="8"/>
+      <x:c r="M18" s="8"/>
+      <x:c r="N18" s="8"/>
+      <x:c r="O18" s="8"/>
+      <x:c r="P18" s="8"/>
+      <x:c r="Q18" s="8"/>
+      <x:c r="R18" s="8"/>
+      <x:c r="S18" s="8"/>
+      <x:c r="T18" s="8"/>
+      <x:c r="U18" s="8"/>
+      <x:c r="V18" s="8"/>
+      <x:c r="W18" s="8"/>
+      <x:c r="X18" s="8"/>
     </x:row>
     <x:row r="19" spans="1:24" ht="15" customHeight="1">
       <x:c r="A19" s="3" t="s">
@@ -736,13 +946,13 @@
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
     <x:oddHeader/>
     <x:oddFooter>&amp;C架空 独立検証
-職務経歴書 ／ 作成日時（JST）：2026年10月29日 01:05&amp;R&amp;P / &amp;N</x:oddFooter>
+職務経歴書 ／ 作成日時（JST）：2026年10月29日 14:12&amp;R&amp;P / &amp;N</x:oddFooter>
     <x:evenHeader/>
     <x:evenFooter>&amp;C架空 独立検証
-職務経歴書 ／ 作成日時（JST）：2026年10月29日 01:05&amp;R&amp;P / &amp;N</x:evenFooter>
+職務経歴書 ／ 作成日時（JST）：2026年10月29日 14:12&amp;R&amp;P / &amp;N</x:evenFooter>
     <x:firstHeader/>
     <x:firstFooter>&amp;C架空 独立検証
-職務経歴書 ／ 作成日時（JST）：2026年10月29日 01:05&amp;R&amp;P / &amp;N</x:firstFooter>
+職務経歴書 ／ 作成日時（JST）：2026年10月29日 14:12&amp;R&amp;P / &amp;N</x:firstFooter>
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
@@ -778,84 +988,304 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A5" s="3" t="s">
+      <x:c r="A5" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="s">
+      <x:c r="B5" s="10"/>
+      <x:c r="C5" s="10"/>
+      <x:c r="D5" s="10"/>
+      <x:c r="E5" s="10"/>
+      <x:c r="F5" s="11"/>
+      <x:c r="G5" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
+      <x:c r="H5" s="10"/>
+      <x:c r="I5" s="10"/>
+      <x:c r="J5" s="10"/>
+      <x:c r="K5" s="10"/>
+      <x:c r="L5" s="10"/>
+      <x:c r="M5" s="10"/>
+      <x:c r="N5" s="10"/>
+      <x:c r="O5" s="10"/>
+      <x:c r="P5" s="10"/>
+      <x:c r="Q5" s="10"/>
+      <x:c r="R5" s="10"/>
+      <x:c r="S5" s="10"/>
+      <x:c r="T5" s="10"/>
+      <x:c r="U5" s="10"/>
+      <x:c r="V5" s="10"/>
+      <x:c r="W5" s="10"/>
+      <x:c r="X5" s="11"/>
     </x:row>
     <x:row r="6" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A6" s="3" t="s">
+      <x:c r="A6" s="4" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="s">
+      <x:c r="B6" s="5"/>
+      <x:c r="C6" s="5"/>
+      <x:c r="D6" s="5"/>
+      <x:c r="E6" s="5"/>
+      <x:c r="F6" s="6"/>
+      <x:c r="G6" s="4" t="s">
         <x:v>19</x:v>
       </x:c>
+      <x:c r="H6" s="5"/>
+      <x:c r="I6" s="5"/>
+      <x:c r="J6" s="5"/>
+      <x:c r="K6" s="5"/>
+      <x:c r="L6" s="5"/>
+      <x:c r="M6" s="5"/>
+      <x:c r="N6" s="5"/>
+      <x:c r="O6" s="5"/>
+      <x:c r="P6" s="5"/>
+      <x:c r="Q6" s="5"/>
+      <x:c r="R6" s="5"/>
+      <x:c r="S6" s="5"/>
+      <x:c r="T6" s="5"/>
+      <x:c r="U6" s="5"/>
+      <x:c r="V6" s="5"/>
+      <x:c r="W6" s="5"/>
+      <x:c r="X6" s="6"/>
     </x:row>
     <x:row r="7" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A7" s="3" t="s">
+      <x:c r="A7" s="4" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G7" s="3" t="s">
+      <x:c r="B7" s="5"/>
+      <x:c r="C7" s="5"/>
+      <x:c r="D7" s="5"/>
+      <x:c r="E7" s="5"/>
+      <x:c r="F7" s="6"/>
+      <x:c r="G7" s="4" t="s">
         <x:v>21</x:v>
       </x:c>
+      <x:c r="H7" s="5"/>
+      <x:c r="I7" s="5"/>
+      <x:c r="J7" s="5"/>
+      <x:c r="K7" s="5"/>
+      <x:c r="L7" s="5"/>
+      <x:c r="M7" s="5"/>
+      <x:c r="N7" s="5"/>
+      <x:c r="O7" s="5"/>
+      <x:c r="P7" s="5"/>
+      <x:c r="Q7" s="5"/>
+      <x:c r="R7" s="5"/>
+      <x:c r="S7" s="5"/>
+      <x:c r="T7" s="5"/>
+      <x:c r="U7" s="5"/>
+      <x:c r="V7" s="5"/>
+      <x:c r="W7" s="5"/>
+      <x:c r="X7" s="6"/>
     </x:row>
     <x:row r="8" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A8" s="3" t="s">
+      <x:c r="A8" s="4" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="B8" s="5"/>
+      <x:c r="C8" s="5"/>
+      <x:c r="D8" s="5"/>
+      <x:c r="E8" s="5"/>
+      <x:c r="F8" s="6"/>
+      <x:c r="G8" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="H8" s="5"/>
+      <x:c r="I8" s="5"/>
+      <x:c r="J8" s="5"/>
+      <x:c r="K8" s="5"/>
+      <x:c r="L8" s="5"/>
+      <x:c r="M8" s="5"/>
+      <x:c r="N8" s="5"/>
+      <x:c r="O8" s="5"/>
+      <x:c r="P8" s="5"/>
+      <x:c r="Q8" s="5"/>
+      <x:c r="R8" s="5"/>
+      <x:c r="S8" s="5"/>
+      <x:c r="T8" s="5"/>
+      <x:c r="U8" s="5"/>
+      <x:c r="V8" s="5"/>
+      <x:c r="W8" s="5"/>
+      <x:c r="X8" s="6"/>
     </x:row>
     <x:row r="9" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A9" s="3" t="s">
+      <x:c r="A9" s="4" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="3" t="s">
+      <x:c r="B9" s="5"/>
+      <x:c r="C9" s="5"/>
+      <x:c r="D9" s="5"/>
+      <x:c r="E9" s="5"/>
+      <x:c r="F9" s="6"/>
+      <x:c r="G9" s="4" t="s">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="H9" s="5"/>
+      <x:c r="I9" s="5"/>
+      <x:c r="J9" s="5"/>
+      <x:c r="K9" s="5"/>
+      <x:c r="L9" s="5"/>
+      <x:c r="M9" s="5"/>
+      <x:c r="N9" s="5"/>
+      <x:c r="O9" s="5"/>
+      <x:c r="P9" s="5"/>
+      <x:c r="Q9" s="5"/>
+      <x:c r="R9" s="5"/>
+      <x:c r="S9" s="5"/>
+      <x:c r="T9" s="5"/>
+      <x:c r="U9" s="5"/>
+      <x:c r="V9" s="5"/>
+      <x:c r="W9" s="5"/>
+      <x:c r="X9" s="6"/>
     </x:row>
     <x:row r="10" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A10" s="3" t="s">
+      <x:c r="A10" s="4" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G10" s="3" t="s">
+      <x:c r="B10" s="5"/>
+      <x:c r="C10" s="5"/>
+      <x:c r="D10" s="5"/>
+      <x:c r="E10" s="5"/>
+      <x:c r="F10" s="6"/>
+      <x:c r="G10" s="4" t="s">
         <x:v>25</x:v>
       </x:c>
+      <x:c r="H10" s="5"/>
+      <x:c r="I10" s="5"/>
+      <x:c r="J10" s="5"/>
+      <x:c r="K10" s="5"/>
+      <x:c r="L10" s="5"/>
+      <x:c r="M10" s="5"/>
+      <x:c r="N10" s="5"/>
+      <x:c r="O10" s="5"/>
+      <x:c r="P10" s="5"/>
+      <x:c r="Q10" s="5"/>
+      <x:c r="R10" s="5"/>
+      <x:c r="S10" s="5"/>
+      <x:c r="T10" s="5"/>
+      <x:c r="U10" s="5"/>
+      <x:c r="V10" s="5"/>
+      <x:c r="W10" s="5"/>
+      <x:c r="X10" s="6"/>
     </x:row>
     <x:row r="11" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A11" s="3" t="s">
+      <x:c r="A11" s="4" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G11" s="3" t="s">
+      <x:c r="B11" s="5"/>
+      <x:c r="C11" s="5"/>
+      <x:c r="D11" s="5"/>
+      <x:c r="E11" s="5"/>
+      <x:c r="F11" s="6"/>
+      <x:c r="G11" s="4" t="s">
         <x:v>27</x:v>
       </x:c>
+      <x:c r="H11" s="5"/>
+      <x:c r="I11" s="5"/>
+      <x:c r="J11" s="5"/>
+      <x:c r="K11" s="5"/>
+      <x:c r="L11" s="5"/>
+      <x:c r="M11" s="5"/>
+      <x:c r="N11" s="5"/>
+      <x:c r="O11" s="5"/>
+      <x:c r="P11" s="5"/>
+      <x:c r="Q11" s="5"/>
+      <x:c r="R11" s="5"/>
+      <x:c r="S11" s="5"/>
+      <x:c r="T11" s="5"/>
+      <x:c r="U11" s="5"/>
+      <x:c r="V11" s="5"/>
+      <x:c r="W11" s="5"/>
+      <x:c r="X11" s="6"/>
     </x:row>
     <x:row r="12" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A12" s="3" t="s">
+      <x:c r="A12" s="4" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G12" s="3" t="s">
+      <x:c r="B12" s="5"/>
+      <x:c r="C12" s="5"/>
+      <x:c r="D12" s="5"/>
+      <x:c r="E12" s="5"/>
+      <x:c r="F12" s="6"/>
+      <x:c r="G12" s="4" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="H12" s="5"/>
+      <x:c r="I12" s="5"/>
+      <x:c r="J12" s="5"/>
+      <x:c r="K12" s="5"/>
+      <x:c r="L12" s="5"/>
+      <x:c r="M12" s="5"/>
+      <x:c r="N12" s="5"/>
+      <x:c r="O12" s="5"/>
+      <x:c r="P12" s="5"/>
+      <x:c r="Q12" s="5"/>
+      <x:c r="R12" s="5"/>
+      <x:c r="S12" s="5"/>
+      <x:c r="T12" s="5"/>
+      <x:c r="U12" s="5"/>
+      <x:c r="V12" s="5"/>
+      <x:c r="W12" s="5"/>
+      <x:c r="X12" s="6"/>
     </x:row>
     <x:row r="13" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A13" s="3" t="s">
+      <x:c r="A13" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G13" s="3" t="s">
+      <x:c r="B13" s="5"/>
+      <x:c r="C13" s="5"/>
+      <x:c r="D13" s="5"/>
+      <x:c r="E13" s="5"/>
+      <x:c r="F13" s="6"/>
+      <x:c r="G13" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
+      <x:c r="H13" s="5"/>
+      <x:c r="I13" s="5"/>
+      <x:c r="J13" s="5"/>
+      <x:c r="K13" s="5"/>
+      <x:c r="L13" s="5"/>
+      <x:c r="M13" s="5"/>
+      <x:c r="N13" s="5"/>
+      <x:c r="O13" s="5"/>
+      <x:c r="P13" s="5"/>
+      <x:c r="Q13" s="5"/>
+      <x:c r="R13" s="5"/>
+      <x:c r="S13" s="5"/>
+      <x:c r="T13" s="5"/>
+      <x:c r="U13" s="5"/>
+      <x:c r="V13" s="5"/>
+      <x:c r="W13" s="5"/>
+      <x:c r="X13" s="6"/>
     </x:row>
     <x:row r="14" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A14" s="3" t="s">
+      <x:c r="A14" s="4" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G14" s="3" t="s">
+      <x:c r="B14" s="5"/>
+      <x:c r="C14" s="5"/>
+      <x:c r="D14" s="5"/>
+      <x:c r="E14" s="5"/>
+      <x:c r="F14" s="6"/>
+      <x:c r="G14" s="4" t="s">
         <x:v>33</x:v>
       </x:c>
+      <x:c r="H14" s="5"/>
+      <x:c r="I14" s="5"/>
+      <x:c r="J14" s="5"/>
+      <x:c r="K14" s="5"/>
+      <x:c r="L14" s="5"/>
+      <x:c r="M14" s="5"/>
+      <x:c r="N14" s="5"/>
+      <x:c r="O14" s="5"/>
+      <x:c r="P14" s="5"/>
+      <x:c r="Q14" s="5"/>
+      <x:c r="R14" s="5"/>
+      <x:c r="S14" s="5"/>
+      <x:c r="T14" s="5"/>
+      <x:c r="U14" s="5"/>
+      <x:c r="V14" s="5"/>
+      <x:c r="W14" s="5"/>
+      <x:c r="X14" s="6"/>
     </x:row>
     <x:row r="15" ht="15" customHeight="1"/>
   </x:sheetData>
@@ -890,13 +1320,13 @@
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
     <x:oddHeader/>
     <x:oddFooter>&amp;C架空 独立検証
-案件経歴 ／ 作成日時（JST）：2026年10月29日 01:05&amp;R&amp;P / &amp;N</x:oddFooter>
+案件経歴 ／ 作成日時（JST）：2026年10月29日 14:12&amp;R&amp;P / &amp;N</x:oddFooter>
     <x:evenHeader/>
     <x:evenFooter>&amp;C架空 独立検証
-案件経歴 ／ 作成日時（JST）：2026年10月29日 01:05&amp;R&amp;P / &amp;N</x:evenFooter>
+案件経歴 ／ 作成日時（JST）：2026年10月29日 14:12&amp;R&amp;P / &amp;N</x:evenFooter>
     <x:firstHeader/>
     <x:firstFooter>&amp;C架空 独立検証
-案件経歴 ／ 作成日時（JST）：2026年10月29日 01:05&amp;R&amp;P / &amp;N</x:firstFooter>
+案件経歴 ／ 作成日時（JST）：2026年10月29日 14:12&amp;R&amp;P / &amp;N</x:firstFooter>
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
